--- a/make_table/jd_self/b1.xlsx
+++ b/make_table/jd_self/b1.xlsx
@@ -496,22 +496,22 @@
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>菜鸟南京江宁行业前置仓2092</t>
+          <t>菜鸟广州白云行业前置仓2221</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>NKG282</t>
+          <t>CAN2127</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>区域仓</t>
+          <t>前置仓</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>江苏省/南京市</t>
+          <t>广东省/广州市</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -618,17 +618,17 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>菜鸟深圳龙华行业前置仓2228</t>
+          <t>菜鸟深圳龙岗行业前置仓2225</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>SZX265</t>
+          <t>SZX263</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>前置仓</t>
+          <t>区域仓</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
@@ -740,12 +740,12 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>菜鸟深圳龙岗行业前置仓2225</t>
+          <t>菜鸟南京江宁行业前置仓2092</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>SZX263</t>
+          <t>NKG282</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>广东省/深圳市</t>
+          <t>江苏省/南京市</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -764,16 +764,16 @@
         </is>
       </c>
       <c r="N4" s="3" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>0.0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="R4" s="3" t="n">
         <v>0.0</v>
@@ -862,22 +862,22 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>菜鸟深圳宝安行业前置仓2226</t>
+          <t>菜鸟杭州萧山行业前置仓2229</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>SZX264</t>
+          <t>HGH2108</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>前置仓</t>
+          <t>区域仓</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>广东省/深圳市</t>
+          <t>浙江省/杭州市</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -886,16 +886,16 @@
         </is>
       </c>
       <c r="N5" s="3" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="O5" s="3" t="n">
         <v>0.0</v>
       </c>
       <c r="P5" s="3" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="Q5" s="3" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="R5" s="3" t="n">
         <v>0.0</v>
@@ -984,22 +984,22 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>菜鸟杭州萧山行业前置仓2229</t>
+          <t>菜鸟深圳宝安行业前置仓2226</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>HGH2108</t>
+          <t>SZX264</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>区域仓</t>
+          <t>前置仓</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>浙江省/杭州市</t>
+          <t>广东省/深圳市</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1008,16 +1008,16 @@
         </is>
       </c>
       <c r="N6" s="3" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>0.0</v>
       </c>
       <c r="P6" s="3" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q6" s="3" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="R6" s="3" t="n">
         <v>0.0</v>
@@ -1106,22 +1106,22 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>顺丰常熟仓</t>
+          <t>菜鸟深圳龙华行业前置仓2228</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>512DCAX</t>
+          <t>SZX265</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>区域仓</t>
+          <t>前置仓</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>江苏省/苏州市</t>
+          <t>广东省/深圳市</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>菜鸟广州白云行业前置仓2221</t>
+          <t>菜鸟杭州下沙行业前置仓2225</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>CAN2127</t>
+          <t>HGH2107</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>广东省/广州市</t>
+          <t>浙江省/杭州市</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1252,16 +1252,16 @@
         </is>
       </c>
       <c r="N8" s="3" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>0.0</v>
       </c>
       <c r="P8" s="3" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="R8" s="3" t="n">
         <v>0.0</v>
@@ -1350,22 +1350,22 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>菜鸟杭州下沙行业前置仓2225</t>
+          <t>顺丰常熟仓</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>HGH2107</t>
+          <t>512DCAX</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>前置仓</t>
+          <t>区域仓</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>浙江省/杭州市</t>
+          <t>江苏省/苏州市</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1374,16 +1374,16 @@
         </is>
       </c>
       <c r="N9" s="3" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="O9" s="3" t="n">
         <v>0.0</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="R9" s="3" t="n">
         <v>0.0</v>
